--- a/score_adaptive_results.xlsx
+++ b/score_adaptive_results.xlsx
@@ -108,15 +108,35 @@
       </c>
       <c r="T1" t="inlineStr">
         <is>
+          <t>P40</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>P50</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>P60</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>P70</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
           <t>P80</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>P90</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>P100</t>
         </is>
@@ -183,12 +203,24 @@
         <v>9.000000</v>
       </c>
       <c r="T2">
+        <v>11.000000</v>
+      </c>
+      <c r="U2">
+        <v>12.000000</v>
+      </c>
+      <c r="V2">
+        <v>13.000000</v>
+      </c>
+      <c r="W2">
+        <v>14.000000</v>
+      </c>
+      <c r="X2">
         <v>19.000000</v>
       </c>
-      <c r="U2">
+      <c r="Y2">
         <v>25.000000</v>
       </c>
-      <c r="V2">
+      <c r="Z2">
         <v>68.000000</v>
       </c>
     </row>
